--- a/laporan_padel_dki_jakarta_2026-09-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-29.xlsx
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp997.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.199.989</t>
+          <t>Rp4.324.989</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-29.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.256.000</t>
+          <t>Rp1.344.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.181.000</t>
+          <t>Rp12.025.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.375.000</t>
+          <t>Rp15.175.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.304.000</t>
+          <t>Rp2.554.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.026.000</t>
+          <t>Rp2.324.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.345.000</t>
+          <t>Rp3.595.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.430.000</t>
+          <t>Rp1.666.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.415.000</t>
+          <t>Rp4.665.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp588.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.420.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.010.000</t>
+          <t>Rp1.210.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.744.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.089.000</t>
+          <t>Rp2.889.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.215.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp1.530.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.720.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>80</v>
       </c>
       <c r="D80" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.610.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.160.000</t>
+          <t>Rp4.840.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp4.186.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp18.100.000</t>
+          <t>Rp18.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp16.950.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>32</v>
       </c>
       <c r="D62" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp235.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp6.417.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.440.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp2.940.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp456.000</t>
+          <t>Rp684.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.440.000</t>
+          <t>Rp12.640.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.915.000</t>
+          <t>Rp12.805.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.831.500</t>
+          <t>Rp14.864.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.630.000</t>
+          <t>Rp6.032.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.525.000</t>
+          <t>Rp11.375.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.916.000</t>
+          <t>Rp2.492.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.275.000</t>
+          <t>Rp26.675.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.215.000</t>
+          <t>Rp8.490.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp310.000</t>
+          <t>Rp620.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.340.000</t>
+          <t>Rp6.440.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.845.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.420.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.324.989</t>
+          <t>Rp4.699.989</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.805.000</t>
+          <t>Rp2.555.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.380.000</t>
+          <t>Rp13.680.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.824.994</t>
+          <t>Rp3.699.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.636.000</t>
+          <t>Rp1.786.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp338.000</t>
+          <t>Rp1.352.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-29.xlsx
@@ -708,12 +708,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.798.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp99.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.025.000</t>
+          <t>Rp12.355.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp438.000</t>
+          <t>Rp1.026.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp689.000</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp5.720.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp1.855.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.510.000</t>
+          <t>Rp2.170.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.510.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>80</v>
       </c>
       <c r="D80" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.030.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.098.004</t>
+          <t>Rp12.074.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp475.000</t>
+          <t>Rp673.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.885.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp2.695.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.186.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp18.550.000</t>
+          <t>Rp19.100.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp338.000</t>
+          <t>Rp716.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.864.000</t>
+          <t>Rp7.656.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp142.000</t>
+          <t>Rp266.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp325.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp12.700.000</t>
+          <t>Rp13.050.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.160.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.105.000</t>
+          <t>Rp4.555.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.640.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp684.000</t>
+          <t>Rp1.020.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.870.000</t>
+          <t>Rp10.310.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>91</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.640.000</t>
+          <t>Rp12.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp12.805.000</t>
+          <t>Rp12.955.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.725.000</t>
+          <t>Rp9.075.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp14.864.500</t>
+          <t>Rp15.034.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.805.000</t>
+          <t>Rp7.255.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.032.000</t>
+          <t>Rp6.630.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.105.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.265.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.375.000</t>
+          <t>Rp11.475.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.492.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7917,14 +7917,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D50" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp105.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -8219,16 +8219,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.030.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.699.989</t>
+          <t>Rp4.449.989</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.680.000</t>
+          <t>Rp13.580.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.030.000</t>
+          <t>Rp4.785.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.715.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.369.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.570.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.605.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.786.000</t>
+          <t>Rp1.986.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-29.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.660.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.699.000</t>
+          <t>Rp2.024.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>160</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.580.000</t>
+          <t>Rp15.180.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.732.991</t>
+          <t>Rp5.128.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.995.000</t>
+          <t>Rp6.495.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.355.000</t>
+          <t>Rp13.180.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.728.000</t>
+          <t>Rp1.152.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.026.000</t>
+          <t>Rp1.464.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.175.000</t>
+          <t>Rp15.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,21 +1381,21 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.554.000</t>
+          <t>Rp2.386.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp180.000</t>
+          <t>Rp70.000 - Rp145.000</t>
         </is>
       </c>
     </row>
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.324.000</t>
+          <t>Rp2.504.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.624.000</t>
+          <t>Rp2.424.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.666.000</t>
+          <t>Rp1.814.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.665.000</t>
+          <t>Rp4.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp588.000</t>
+          <t>Rp2.148.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.998.000</t>
+          <t>Rp798.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.210.000</t>
+          <t>Rp1.610.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.805.000</t>
+          <t>Rp5.045.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp4.896.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.182.000</t>
+          <t>Rp8.972.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.782.000</t>
+          <t>Rp5.280.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.510.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>96</v>
       </c>
       <c r="D79" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>80</v>
       </c>
       <c r="D80" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>68</v>
       </c>
       <c r="D97" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.695.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp2.990.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.296.184</t>
+          <t>Rp2.693.672</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp16.950.000</t>
+          <t>Rp17.550.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.656.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>72</v>
       </c>
       <c r="D56" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp266.000</t>
+          <t>Rp319.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>80</v>
       </c>
       <c r="D68" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp7.440.000</t>
+          <t>Rp7.790.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp13.050.000</t>
+          <t>Rp13.600.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp640.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.582.500</t>
+          <t>Rp14.547.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.730.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.940.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.555.000</t>
+          <t>Rp4.270.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.248.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.310.000</t>
+          <t>Rp10.390.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>91</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.240.000</t>
+          <t>Rp12.640.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp9.425.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.255.000</t>
+          <t>Rp7.805.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp5.325.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.675.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.800.000</t>
+          <t>Rp24.100.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.636.000</t>
+          <t>Rp7.461.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.265.000</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.475.000</t>
+          <t>Rp11.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp4.468.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.568.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp10.249.000</t>
+          <t>Rp11.049.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.490.000</t>
+          <t>Rp8.890.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp27.350.000</t>
+          <t>Rp29.550.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp6.420.000</t>
+          <t>Rp5.620.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp4.270.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp620.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.845.000</t>
+          <t>Rp2.315.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.445.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp2.170.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.930.000</t>
+          <t>Rp6.420.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.449.989</t>
+          <t>Rp4.649.988</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp825.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.530.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.580.000</t>
+          <t>Rp14.540.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.785.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.955.000</t>
+          <t>Rp2.503.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.699.994</t>
+          <t>Rp3.899.993</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.570.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp415.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp3.580.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.370.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp3.270.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.732.000</t>
+          <t>Rp3.136.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.986.000</t>
+          <t>Rp2.283.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.352.000</t>
+          <t>Rp1.859.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-29.xlsx
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.170.000</t>
+          <t>Rp2.490.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.074.004</t>
+          <t>Rp12.273.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.515.000</t>
+          <t>Rp2.615.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.990.000</t>
+          <t>Rp2.185.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp575.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.630.000</t>
+          <t>Rp6.830.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.725.000</t>
+          <t>Rp11.975.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.468.000</t>
+          <t>Rp5.032.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.479.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.270.000</t>
+          <t>Rp4.570.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.445.000</t>
+          <t>Rp1.745.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.649.988</t>
+          <t>Rp4.774.988</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.540.000</t>
+          <t>Rp14.840.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.899.993</t>
+          <t>Rp4.024.993</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.570.000</t>
+          <t>Rp2.785.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
